--- a/a_materials/Lab Schedule.xlsx
+++ b/a_materials/Lab Schedule.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adamsoliman/Documents/GitHub/Econometrics-Slides/a_materials/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19FCFFB8-283C-644D-A4A9-056EFEA4A08C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{626AC8AB-9A4A-0A4B-9077-4BFCEBF48524}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="700" windowWidth="27040" windowHeight="15180" xr2:uid="{1103A02E-6F1A-EC41-B75E-F74E9889530B}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17200" xr2:uid="{1103A02E-6F1A-EC41-B75E-F74E9889530B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,10 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
-  <si>
-    <t>Date</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
   <si>
     <t>Help with final project</t>
   </si>
@@ -52,12 +49,6 @@
     <t>Regression</t>
   </si>
   <si>
-    <t>Regression Discontinuity</t>
-  </si>
-  <si>
-    <t>RCTs</t>
-  </si>
-  <si>
     <t xml:space="preserve">Lab </t>
   </si>
   <si>
@@ -73,13 +64,25 @@
     <t>No Lab (Election Day)</t>
   </si>
   <si>
-    <t>Difference-in-Differences</t>
-  </si>
-  <si>
     <t>No Lab (Thanksgiving)</t>
   </si>
   <si>
     <t>Panel Data</t>
+  </si>
+  <si>
+    <t>Week Starting</t>
+  </si>
+  <si>
+    <t>Sampling</t>
+  </si>
+  <si>
+    <t>RCTs + Regression Intro</t>
+  </si>
+  <si>
+    <t>Difference-in-Differences + RD</t>
+  </si>
+  <si>
+    <t>Confidence Intervals, Hypothesis Testing and Regression Inference</t>
   </si>
 </sst>
 </file>
@@ -453,7 +456,7 @@
   <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="63.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="10.83203125" style="1"/>
@@ -461,184 +464,184 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D1" s="3"/>
     </row>
     <row r="2" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
-        <v>45531</v>
+        <v>46258</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <f>A2+7</f>
-        <v>45538</v>
+        <v>46265</v>
       </c>
       <c r="B3" s="1">
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <f t="shared" ref="A4:A15" si="0">A3+7</f>
-        <v>45545</v>
+        <v>46272</v>
       </c>
       <c r="B4" s="1">
         <v>3</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <f t="shared" si="0"/>
-        <v>45552</v>
+        <v>46279</v>
       </c>
       <c r="B5" s="1">
         <v>4</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <f t="shared" si="0"/>
-        <v>45559</v>
+        <v>46286</v>
       </c>
       <c r="B6" s="1">
         <v>5</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <f t="shared" si="0"/>
-        <v>45566</v>
+        <v>46293</v>
       </c>
       <c r="B7" s="1">
         <v>6</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <f t="shared" si="0"/>
-        <v>45573</v>
+        <v>46300</v>
       </c>
       <c r="B8" s="1">
         <v>7</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <f t="shared" si="0"/>
-        <v>45580</v>
+        <v>46307</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <f t="shared" si="0"/>
-        <v>45587</v>
+        <v>46314</v>
       </c>
       <c r="B10" s="1">
         <v>8</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <f t="shared" si="0"/>
-        <v>45594</v>
+        <v>46321</v>
       </c>
       <c r="B11" s="1">
         <v>9</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <f t="shared" si="0"/>
-        <v>45601</v>
+        <v>46328</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <f t="shared" si="0"/>
-        <v>45608</v>
+        <v>46335</v>
       </c>
       <c r="B13" s="1">
         <v>10</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <f t="shared" si="0"/>
-        <v>45615</v>
+        <v>46342</v>
       </c>
       <c r="B14" s="1">
         <v>11</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <f t="shared" si="0"/>
-        <v>45622</v>
+        <v>46349</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <f>A15+7</f>
-        <v>45629</v>
+        <v>46356</v>
       </c>
       <c r="B16" s="1">
         <v>12</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.2">
